--- a/fuente/plantilla/parte.xlsx
+++ b/fuente/plantilla/parte.xlsx
@@ -195,7 +195,7 @@
     <t>Cloruro Calcico</t>
   </si>
   <si>
-    <t>E.C. RECICLADA</t>
+    <t>P.H. BALSA</t>
   </si>
   <si>
     <t>INCR. RECICLADA</t>
